--- a/工时/工时4月-李广飞.xlsx
+++ b/工时/工时4月-李广飞.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
   <si>
     <t>周一</t>
   </si>
@@ -60,6 +60,24 @@
   </si>
   <si>
     <t>公众号接口功能调研</t>
+  </si>
+  <si>
+    <t>bug修复</t>
+  </si>
+  <si>
+    <t>公众号接口创建</t>
+  </si>
+  <si>
+    <t>精炼文章核对</t>
+  </si>
+  <si>
+    <t>pipeline搭建</t>
+  </si>
+  <si>
+    <t>特刊检索功能开发</t>
+  </si>
+  <si>
+    <t>封装集成</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1036,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.3916666666667" customWidth="1"/>
@@ -1076,8 +1094,8 @@
         <v>0</v>
       </c>
       <c r="J2" s="3">
-        <f>SUM(I2:I35)</f>
-        <v>6</v>
+        <f>SUM(I2:I28)</f>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="2:8">
@@ -1112,8 +1130,8 @@
         <v>45760</v>
       </c>
       <c r="I4">
-        <f>SUM(B5:H12)</f>
-        <v>6</v>
+        <f>SUM(B5:H10)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1125,7 +1143,7 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -1160,7 +1178,10 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1169,7 +1190,10 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1178,234 +1202,273 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="2:8">
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="2:8">
+    <row r="11" spans="2:9">
+      <c r="B11" s="1">
+        <v>45761</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45762</v>
+      </c>
+      <c r="D11" s="1">
+        <v>45763</v>
+      </c>
+      <c r="E11" s="1">
+        <v>45764</v>
+      </c>
+      <c r="F11" s="1">
+        <v>45765</v>
+      </c>
+      <c r="G11" s="1">
+        <v>45766</v>
+      </c>
+      <c r="H11" s="1">
+        <v>45767</v>
+      </c>
+      <c r="I11">
+        <f>SUM(B12:H15)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="1">
-        <v>45761</v>
-      </c>
-      <c r="C13" s="1">
-        <v>45762</v>
-      </c>
-      <c r="D13" s="1">
-        <v>45763</v>
-      </c>
-      <c r="E13" s="1">
-        <v>45764</v>
-      </c>
-      <c r="F13" s="1">
-        <v>45765</v>
-      </c>
-      <c r="G13" s="1">
-        <v>45766</v>
-      </c>
-      <c r="H13" s="1">
-        <v>45767</v>
-      </c>
-      <c r="I13">
-        <f>SUM(B14:H20)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="2:8">
+    <row r="16" spans="2:9">
+      <c r="B16" s="1">
+        <v>45768</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45769</v>
+      </c>
+      <c r="D16" s="1">
+        <v>45770</v>
+      </c>
+      <c r="E16" s="1">
+        <v>45771</v>
+      </c>
+      <c r="F16" s="1">
+        <v>45772</v>
+      </c>
+      <c r="G16" s="1">
+        <v>45773</v>
+      </c>
+      <c r="H16" s="1">
+        <v>45774</v>
+      </c>
+      <c r="I16">
+        <f>SUM(B17:H21)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="2">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="E20" s="2">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="1">
-        <v>45768</v>
-      </c>
-      <c r="C21" s="1">
-        <v>45769</v>
-      </c>
-      <c r="D21" s="1">
-        <v>45770</v>
-      </c>
-      <c r="E21" s="1">
-        <v>45771</v>
-      </c>
-      <c r="F21" s="1">
-        <v>45772</v>
-      </c>
-      <c r="G21" s="1">
-        <v>45773</v>
-      </c>
-      <c r="H21" s="1">
-        <v>45774</v>
-      </c>
-      <c r="I21">
-        <f>SUM(B22:H27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="1">
+      <c r="H20" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="1">
         <v>45775</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C22" s="1">
         <v>45776</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D22" s="1">
         <v>45777</v>
       </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29">
-        <f>SUM(B30:H34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22">
+        <f>SUM(B23:H27)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
